--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2CB53732CD90A3B6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78C07405-E76C-444A-BB01-421A5F7E83B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wochenplan" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,6 @@
     <t>14:00–15:00</t>
   </si>
   <si>
-    <t>4495 RUST (Ü, 1. PG) · Raum: C5-11
-2031 Algorithmen Datenstrukt (V, 1. PG) · Raum: H8</t>
-  </si>
-  <si>
     <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
 4130-P-748 VHDL (P, 1. PG) · Raum: C5-11</t>
   </si>
@@ -153,10 +149,6 @@
     <t>15:00–16:00</t>
   </si>
   <si>
-    <t>4491 RUST (V, 1. PG) · Raum: C5-14
-2031 Algorithmen Datenstrukt (V, 1. PG) · Raum: H8</t>
-  </si>
-  <si>
     <t>4840-P Fahrzeugelektronik (P, 1. PG) · Raum: C6-10</t>
   </si>
   <si>
@@ -164,12 +156,6 @@
   </si>
   <si>
     <t>4051 VHDL (V, 1. PG) · Raum: C5-14</t>
-  </si>
-  <si>
-    <t>4491 RUST (V, 1. PG) · Raum: C5-14
-2035 Algorithmen Datenstr (Ü, 1. PG) · Raum: H8
-4010-P Industrieroboter (P, 1. PG) · Raum: D3-05
-1511-GU Klimawandel und globale Umweltveränderungen (S, 1. PG) · Raum: H6</t>
   </si>
   <si>
     <t>17:00–18:00</t>
@@ -215,6 +201,20 @@
   </si>
   <si>
     <t>4015 Industrieroboter (Ü, 1. PG) · Raum: D3-33</t>
+  </si>
+  <si>
+    <t>4491 RUST (V, 1. PG) · Raum: C5-14
+2035 Algorithmen und Datenstrukturen (Ü, 1. PG) · Raum: H8
+4010-P Industrieroboter (P, 1. PG) · Raum: D3-05
+1511-GU Klimawandel und globale Umweltveränderungen (S, 1. PG) · Raum: H6</t>
+  </si>
+  <si>
+    <t>4491 RUST (V, 1. PG) · Raum: C5-14
+2031 Algorithmen und Datenstrukturen (V, 1. PG) · Raum: H8</t>
+  </si>
+  <si>
+    <t>4495 RUST (Ü, 1. PG) · Raum: C5-11
+2031 Algorithmen und Datenstrukturen (V, 1. PG) · Raum: H8</t>
   </si>
 </sst>
 </file>
@@ -364,6 +364,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,15 +384,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -606,24 +606,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="19.2" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -646,242 +646,242 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A14" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="100.05" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.55" customHeight="1">
+      <c r="A18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="100.05" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.05" customHeight="1">
+      <c r="A19" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="17.55" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.05" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
